--- a/Milestone 3/ChecklistDeControloDeArtefactos.xlsx
+++ b/Milestone 3/ChecklistDeControloDeArtefactos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gonçalo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilizador\OneDrive\Documentos\GitHub\LDS\Milestone 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED3E452-31E6-4C43-A0E6-2689F1D15EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CCBF17-BAA5-4EE7-BF30-71DC2B2AFEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" activeTab="2" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Milestone 1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="149">
   <si>
     <t>Nome</t>
   </si>
@@ -483,6 +483,9 @@
   </si>
   <si>
     <t>Guia de Utilizador (apenas amostra)</t>
+  </si>
+  <si>
+    <t>coverage-report.zip</t>
   </si>
 </sst>
 </file>
@@ -1001,19 +1004,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81452DF3-ED1F-4F46-BA76-8CFF15181C87}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="38.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="54.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.15625" style="1"/>
+    <col min="2" max="2" width="38.83984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="54.15625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.41796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.15625" style="1"/>
+    <col min="6" max="6" width="11.26171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.68359375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.15625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1021,7 +1024,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3"/>
       <c r="B2" s="14" t="s">
         <v>0</v>
@@ -1043,7 +1046,7 @@
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3"/>
       <c r="B3" s="17" t="s">
         <v>5</v>
@@ -1065,7 +1068,7 @@
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3"/>
       <c r="B4" s="17" t="s">
         <v>6</v>
@@ -1087,7 +1090,7 @@
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3"/>
       <c r="B5" s="17" t="s">
         <v>8</v>
@@ -1109,7 +1112,7 @@
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3"/>
       <c r="B6" s="17" t="s">
         <v>10</v>
@@ -1131,7 +1134,7 @@
       </c>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3"/>
       <c r="B7" s="17" t="s">
         <v>12</v>
@@ -1153,7 +1156,7 @@
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3"/>
       <c r="B8" s="17" t="s">
         <v>13</v>
@@ -1175,7 +1178,7 @@
       </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3"/>
       <c r="B9" s="17" t="s">
         <v>15</v>
@@ -1197,7 +1200,7 @@
       </c>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3"/>
       <c r="B10" s="17" t="s">
         <v>17</v>
@@ -1219,7 +1222,7 @@
       </c>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="41.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3"/>
       <c r="B11" s="17" t="s">
         <v>19</v>
@@ -1241,7 +1244,7 @@
       </c>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3"/>
       <c r="B12" s="17" t="s">
         <v>20</v>
@@ -1261,7 +1264,7 @@
       <c r="G12" s="5"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -1278,19 +1281,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A66EA39F-753F-4FFE-94B6-3459E370B3FE}">
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="13.8" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="8"/>
-    <col min="2" max="2" width="38.85546875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="54.140625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="8"/>
-    <col min="6" max="6" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.15625" style="8"/>
+    <col min="2" max="2" width="38.83984375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="54.15625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="12.41796875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="9.15625" style="8"/>
+    <col min="6" max="6" width="11.578125" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" style="8" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="8"/>
+    <col min="8" max="16384" width="9.15625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1298,7 +1301,7 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="10"/>
       <c r="B2" s="15" t="s">
         <v>0</v>
@@ -1320,7 +1323,7 @@
       </c>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="10"/>
       <c r="B3" s="5" t="s">
         <v>98</v>
@@ -1342,7 +1345,7 @@
       </c>
       <c r="H3" s="12"/>
     </row>
-    <row r="4" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10"/>
       <c r="B4" s="5" t="s">
         <v>29</v>
@@ -1367,7 +1370,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="10"/>
       <c r="B5" s="5" t="s">
         <v>30</v>
@@ -1392,7 +1395,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="10"/>
       <c r="B6" s="5" t="s">
         <v>31</v>
@@ -1417,7 +1420,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="10"/>
       <c r="B7" s="5" t="s">
         <v>32</v>
@@ -1442,7 +1445,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="10"/>
       <c r="B8" s="5" t="s">
         <v>73</v>
@@ -1467,7 +1470,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A9" s="10"/>
       <c r="B9" s="5" t="s">
         <v>74</v>
@@ -1489,7 +1492,7 @@
       </c>
       <c r="H9" s="12"/>
     </row>
-    <row r="10" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A10" s="10"/>
       <c r="B10" s="5" t="s">
         <v>75</v>
@@ -1511,7 +1514,7 @@
       </c>
       <c r="H10" s="12"/>
     </row>
-    <row r="11" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
         <v>128</v>
@@ -1533,7 +1536,7 @@
       </c>
       <c r="H11" s="12"/>
     </row>
-    <row r="12" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="41.4" x14ac:dyDescent="0.45">
       <c r="A12" s="10"/>
       <c r="B12" s="5" t="s">
         <v>76</v>
@@ -1555,7 +1558,7 @@
       </c>
       <c r="H12" s="12"/>
     </row>
-    <row r="13" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A13" s="10"/>
       <c r="B13" s="5" t="s">
         <v>78</v>
@@ -1577,7 +1580,7 @@
       </c>
       <c r="H13" s="12"/>
     </row>
-    <row r="14" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A14" s="10"/>
       <c r="B14" s="5" t="s">
         <v>79</v>
@@ -1599,7 +1602,7 @@
       </c>
       <c r="H14" s="12"/>
     </row>
-    <row r="15" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A15" s="10"/>
       <c r="B15" s="5" t="s">
         <v>80</v>
@@ -1621,7 +1624,7 @@
       </c>
       <c r="H15" s="12"/>
     </row>
-    <row r="16" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A16" s="10"/>
       <c r="B16" s="5" t="s">
         <v>92</v>
@@ -1643,7 +1646,7 @@
       </c>
       <c r="H16" s="12"/>
     </row>
-    <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="10"/>
       <c r="B17" s="5" t="s">
         <v>77</v>
@@ -1665,7 +1668,7 @@
       </c>
       <c r="H17" s="12"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="10"/>
       <c r="B18" s="5" t="s">
         <v>129</v>
@@ -1687,7 +1690,7 @@
       </c>
       <c r="H18" s="12"/>
     </row>
-    <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A19" s="10"/>
       <c r="B19" s="5" t="s">
         <v>130</v>
@@ -1709,7 +1712,7 @@
       </c>
       <c r="H19" s="12"/>
     </row>
-    <row r="20" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A20" s="10"/>
       <c r="B20" s="5" t="s">
         <v>95</v>
@@ -1731,7 +1734,7 @@
       </c>
       <c r="H20" s="12"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A21" s="10"/>
       <c r="B21" s="5" t="s">
         <v>94</v>
@@ -1753,7 +1756,7 @@
       </c>
       <c r="H21" s="12"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="10"/>
       <c r="B22" s="5" t="s">
         <v>33</v>
@@ -1775,7 +1778,7 @@
       </c>
       <c r="H22" s="12"/>
     </row>
-    <row r="23" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="10"/>
       <c r="B23" s="5" t="s">
         <v>34</v>
@@ -1797,7 +1800,7 @@
       </c>
       <c r="H23" s="12"/>
     </row>
-    <row r="24" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="41.4" x14ac:dyDescent="0.45">
       <c r="B24" s="5" t="s">
         <v>36</v>
       </c>
@@ -1825,20 +1828,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C861563-C733-47ED-8179-10C65DB83741}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="13.8" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="8"/>
-    <col min="2" max="2" width="38.85546875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="54.140625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="8"/>
-    <col min="6" max="6" width="11.140625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" style="8" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="9.15625" style="8"/>
+    <col min="2" max="2" width="38.83984375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="54.15625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="12.41796875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="9.15625" style="8"/>
+    <col min="6" max="6" width="11.15625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="20.83984375" style="8" customWidth="1"/>
+    <col min="8" max="16384" width="9.15625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1846,7 +1849,7 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
     </row>
-    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="10"/>
       <c r="B2" s="11" t="s">
         <v>0</v>
@@ -1868,7 +1871,7 @@
       </c>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="10"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1889,11 +1892,9 @@
         <v>115</v>
       </c>
       <c r="H3" s="12"/>
-      <c r="K3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="K3"/>
+    </row>
+    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A4" s="10"/>
       <c r="B4" s="5" t="s">
         <v>44</v>
@@ -1915,7 +1916,7 @@
       </c>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A5" s="10"/>
       <c r="B5" s="5" t="s">
         <v>45</v>
@@ -1937,7 +1938,7 @@
       </c>
       <c r="H5" s="12"/>
     </row>
-    <row r="6" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A6" s="10"/>
       <c r="B6" s="5" t="s">
         <v>46</v>
@@ -1959,7 +1960,7 @@
       </c>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="10"/>
       <c r="B7" s="5" t="s">
         <v>47</v>
@@ -1981,7 +1982,7 @@
       </c>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="10"/>
       <c r="B8" s="5" t="s">
         <v>48</v>
@@ -2003,7 +2004,7 @@
       </c>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A9" s="10"/>
       <c r="B9" s="5" t="s">
         <v>49</v>
@@ -2025,7 +2026,7 @@
       </c>
       <c r="H9" s="12"/>
     </row>
-    <row r="10" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A10" s="10"/>
       <c r="B10" s="5" t="s">
         <v>50</v>
@@ -2047,14 +2048,12 @@
       </c>
       <c r="H10" s="12"/>
     </row>
-    <row r="11" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>42</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
         <v>40</v>
       </c>
@@ -2062,19 +2061,41 @@
         <v>22</v>
       </c>
       <c r="F11" s="19">
+        <v>45967</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:11" ht="41.4" x14ac:dyDescent="0.45">
+      <c r="A12" s="10"/>
+      <c r="B12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="19">
         <v>45966</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2085,19 +2106,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4906293-B838-4C65-80DE-8D6330669CCD}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="38.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="54.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.15625" style="1"/>
+    <col min="2" max="2" width="38.83984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="54.15625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.41796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.15625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.26171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.68359375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.15625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2105,7 +2126,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A2" s="3"/>
       <c r="B2" s="7" t="s">
         <v>0</v>
@@ -2127,7 +2148,7 @@
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
         <v>59</v>
@@ -2152,7 +2173,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
         <v>60</v>
@@ -2177,7 +2198,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3"/>
       <c r="B5" s="5" t="s">
         <v>61</v>
@@ -2202,7 +2223,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
         <v>47</v>
@@ -2227,7 +2248,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3"/>
       <c r="B7" s="5" t="s">
         <v>62</v>
@@ -2252,7 +2273,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3"/>
       <c r="B8" s="5" t="s">
         <v>63</v>
@@ -2277,7 +2298,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3"/>
       <c r="B9" s="16" t="s">
         <v>90</v>
@@ -2299,7 +2320,7 @@
       </c>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
         <v>64</v>
@@ -2321,7 +2342,7 @@
       </c>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="41.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3"/>
       <c r="B11" s="5" t="s">
         <v>36</v>
@@ -2343,7 +2364,7 @@
       </c>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>

--- a/Milestone 3/ChecklistDeControloDeArtefactos.xlsx
+++ b/Milestone 3/ChecklistDeControloDeArtefactos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilizador\OneDrive\Documentos\GitHub\LDS\Milestone 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CCBF17-BAA5-4EE7-BF30-71DC2B2AFEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B5B161-598C-428A-AE22-7C8B089BAE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" activeTab="2" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" activeTab="3" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Milestone 1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="144">
   <si>
     <t>Nome</t>
   </si>
@@ -447,21 +447,6 @@
   </si>
   <si>
     <t>Mockups.pdf</t>
-  </si>
-  <si>
-    <t>Critérios de Qualidade de Requisitos</t>
-  </si>
-  <si>
-    <t>Especificação de Requisitos de Software</t>
-  </si>
-  <si>
-    <t>Registo de Aprovação de Requisitos</t>
-  </si>
-  <si>
-    <t>Protótipo de Interfaces (UI/UX)</t>
-  </si>
-  <si>
-    <t>Guia de Estilo de codificação</t>
   </si>
   <si>
     <t>Relatório de Cobertura de Testes (backend)</t>
@@ -634,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -669,6 +654,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1366,9 +1352,7 @@
         <v>108</v>
       </c>
       <c r="H4" s="12"/>
-      <c r="M4" t="s">
-        <v>136</v>
-      </c>
+      <c r="M4"/>
     </row>
     <row r="5" spans="1:13" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="10"/>
@@ -1391,9 +1375,7 @@
         <v>109</v>
       </c>
       <c r="H5" s="12"/>
-      <c r="M5" t="s">
-        <v>137</v>
-      </c>
+      <c r="M5"/>
     </row>
     <row r="6" spans="1:13" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="10"/>
@@ -1416,9 +1398,7 @@
         <v>135</v>
       </c>
       <c r="H6" s="12"/>
-      <c r="M6" t="s">
-        <v>138</v>
-      </c>
+      <c r="M6"/>
     </row>
     <row r="7" spans="1:13" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="10"/>
@@ -1441,9 +1421,7 @@
         <v>110</v>
       </c>
       <c r="H7" s="12"/>
-      <c r="M7" t="s">
-        <v>139</v>
-      </c>
+      <c r="M7"/>
     </row>
     <row r="8" spans="1:13" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="10"/>
@@ -1466,9 +1444,7 @@
         <v>111</v>
       </c>
       <c r="H8" s="12"/>
-      <c r="M8" t="s">
-        <v>140</v>
-      </c>
+      <c r="M8"/>
     </row>
     <row r="9" spans="1:13" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A9" s="10"/>
@@ -2051,7 +2027,7 @@
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
@@ -2064,7 +2040,7 @@
         <v>45967</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H11" s="12"/>
     </row>
@@ -2105,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4906293-B838-4C65-80DE-8D6330669CCD}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9.15625" style="1"/>
@@ -2170,7 +2146,7 @@
       </c>
       <c r="H3" s="4"/>
       <c r="K3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -2195,7 +2171,7 @@
       </c>
       <c r="H4" s="4"/>
       <c r="K4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
@@ -2220,7 +2196,7 @@
       </c>
       <c r="H5" s="4"/>
       <c r="K5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -2245,7 +2221,7 @@
       </c>
       <c r="H6" s="4"/>
       <c r="K6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -2270,7 +2246,7 @@
       </c>
       <c r="H7" s="4"/>
       <c r="K7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
@@ -2295,7 +2271,7 @@
       </c>
       <c r="H8" s="4"/>
       <c r="K8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
@@ -2365,12 +2341,119 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="19">
+        <v>45994</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3"/>
+      <c r="B13" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="19">
+        <v>45994</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3"/>
+      <c r="B14" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="19">
+        <v>45994</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3"/>
+      <c r="B15" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="19">
+        <v>45994</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3"/>
+      <c r="B16" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="19">
+        <v>45994</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3"/>
+      <c r="B17" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="19">
+        <v>45994</v>
+      </c>
+      <c r="G17" s="20"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Milestone 3/ChecklistDeControloDeArtefactos.xlsx
+++ b/Milestone 3/ChecklistDeControloDeArtefactos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilizador\OneDrive\Documentos\GitHub\LDS\Milestone 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B5B161-598C-428A-AE22-7C8B089BAE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6489BD01-746E-4637-AAC9-7260D7F515D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" activeTab="3" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" activeTab="2" xr2:uid="{C27BD991-62B3-4544-9BD0-0998C100EC3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Milestone 1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="149">
   <si>
     <t>Nome</t>
   </si>
@@ -389,15 +389,6 @@
     <t>/Backend</t>
   </si>
   <si>
-    <t>TestesDeIntegracao.docx</t>
-  </si>
-  <si>
-    <t>TestesUnitarios.docx</t>
-  </si>
-  <si>
-    <t>RequestsPostman.docx</t>
-  </si>
-  <si>
     <t>PipelineCI/CD.docx</t>
   </si>
   <si>
@@ -470,7 +461,31 @@
     <t>Guia de Utilizador (apenas amostra)</t>
   </si>
   <si>
-    <t>coverage-report.zip</t>
+    <t>\codigo\ConsultaPlus.Tests</t>
+  </si>
+  <si>
+    <t>\codigo\ConsultaPlus.Tests\Integracao</t>
+  </si>
+  <si>
+    <t>RequestsPostman</t>
+  </si>
+  <si>
+    <t>RequirementsTraceabilityMatrixV2.0.xlsx</t>
+  </si>
+  <si>
+    <t>coverage-report-unit.zip e coverage-report-integration.zip</t>
+  </si>
+  <si>
+    <t>Pasta zipada com os relatorios de cobertura dos testes</t>
+  </si>
+  <si>
+    <t>Concluido</t>
+  </si>
+  <si>
+    <t>Diogo Silva</t>
+  </si>
+  <si>
+    <t>Diogo Silva e Guilherme Barreiro</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1241,7 @@
         <v>45923</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H11" s="4"/>
     </row>
@@ -1395,7 +1410,7 @@
         <v>45938</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H6" s="12"/>
       <c r="M6"/>
@@ -1493,7 +1508,7 @@
     <row r="11" spans="1:13" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>84</v>
@@ -1647,10 +1662,10 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="10"/>
       <c r="B18" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>23</v>
@@ -1669,10 +1684,10 @@
     <row r="19" spans="1:8" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A19" s="10"/>
       <c r="B19" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>23</v>
@@ -1684,7 +1699,7 @@
         <v>45938</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H19" s="12"/>
     </row>
@@ -1772,7 +1787,7 @@
         <v>45938</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H23" s="12"/>
     </row>
@@ -1793,7 +1808,7 @@
         <v>45938</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1826,7 @@
     <col min="2" max="2" width="38.83984375" style="8" customWidth="1"/>
     <col min="3" max="3" width="54.15625" style="8" customWidth="1"/>
     <col min="4" max="4" width="12.41796875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9.15625" style="8"/>
+    <col min="5" max="5" width="10.41796875" style="8" customWidth="1"/>
     <col min="6" max="6" width="11.15625" style="8" customWidth="1"/>
     <col min="7" max="7" width="20.83984375" style="8" customWidth="1"/>
     <col min="8" max="16384" width="9.15625" style="8"/>
@@ -1856,7 +1871,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>22</v>
@@ -1879,7 +1894,7 @@
         <v>52</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>22</v>
@@ -1888,7 +1903,7 @@
         <v>45966</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="H4" s="12"/>
     </row>
@@ -1901,7 +1916,7 @@
         <v>53</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>22</v>
@@ -1910,7 +1925,7 @@
         <v>45966</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="H5" s="12"/>
     </row>
@@ -1923,16 +1938,16 @@
         <v>54</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F6" s="19">
         <v>45966</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="H6" s="12"/>
     </row>
@@ -1945,20 +1960,20 @@
         <v>55</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="F7" s="19">
         <v>45966</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A8" s="10"/>
       <c r="B8" s="5" t="s">
         <v>48</v>
@@ -1967,16 +1982,16 @@
         <v>56</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="F8" s="19">
         <v>45966</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="H8" s="12"/>
     </row>
@@ -1998,7 +2013,7 @@
         <v>45966</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H9" s="12"/>
     </row>
@@ -2020,31 +2035,33 @@
         <v>45966</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H10" s="12"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" ht="41.4" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" s="5"/>
+        <v>133</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="D11" s="5" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="F11" s="19">
         <v>45967</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H11" s="12"/>
     </row>
-    <row r="12" spans="1:11" ht="41.4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" ht="55.2" x14ac:dyDescent="0.45">
       <c r="A12" s="10"/>
       <c r="B12" s="5" t="s">
         <v>36</v>
@@ -2053,16 +2070,16 @@
         <v>42</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="F12" s="19">
         <v>45966</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H12" s="12"/>
     </row>
@@ -2142,11 +2159,11 @@
         <v>45994</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H3" s="4"/>
       <c r="K3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -2167,11 +2184,11 @@
         <v>45994</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H4" s="4"/>
       <c r="K4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
@@ -2192,11 +2209,11 @@
         <v>45994</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H5" s="4"/>
       <c r="K5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -2217,11 +2234,11 @@
         <v>45994</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H6" s="4"/>
       <c r="K6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -2246,7 +2263,7 @@
       </c>
       <c r="H7" s="4"/>
       <c r="K7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
@@ -2267,11 +2284,11 @@
         <v>45994</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H8" s="4"/>
       <c r="K8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.55000000000000004">
@@ -2314,7 +2331,7 @@
         <v>45994</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H10" s="4"/>
     </row>
@@ -2336,14 +2353,14 @@
         <v>45994</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3"/>
       <c r="B12" s="20" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="5" t="s">
@@ -2361,7 +2378,7 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3"/>
       <c r="B13" s="20" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="5" t="s">
@@ -2379,7 +2396,7 @@
     <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3"/>
       <c r="B14" s="20" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="5" t="s">
@@ -2397,7 +2414,7 @@
     <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3"/>
       <c r="B15" s="20" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="5" t="s">
@@ -2415,7 +2432,7 @@
     <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3"/>
       <c r="B16" s="20" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="5" t="s">
@@ -2433,7 +2450,7 @@
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3"/>
       <c r="B17" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="5" t="s">
